--- a/InputData/indst/BCoISC/BAU Cost of Industry Sector Capital.xlsx
+++ b/InputData/indst/BCoISC/BAU Cost of Industry Sector Capital.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\BCoISC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568C2CCC-14D7-4413-86D9-0AFAA70D7DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7933CDE8-D7C9-4BD7-B3C3-CB6565BCCC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="495" windowWidth="25245" windowHeight="16245" tabRatio="644" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="644" activeTab="3" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="NYU Data" sheetId="7" r:id="rId2"/>
     <sheet name="EPS &lt;&gt; NYU Industry CoC Map" sheetId="8" r:id="rId3"/>
-    <sheet name="EPS &lt;&gt; NYU Industry CoD Map" sheetId="10" r:id="rId4"/>
-    <sheet name="BCoISC-WACCbI" sheetId="3" r:id="rId5"/>
-    <sheet name="BCoISC-FIRbI" sheetId="9" r:id="rId6"/>
-    <sheet name="BCoISC-RPfE" sheetId="4" r:id="rId7"/>
+    <sheet name="Pretax WACC Build" sheetId="11" r:id="rId4"/>
+    <sheet name="EPS &lt;&gt; NYU Industry CoD Map" sheetId="10" r:id="rId5"/>
+    <sheet name="BCoISC-WACCbI" sheetId="3" r:id="rId6"/>
+    <sheet name="BCoISC-FIRbI" sheetId="9" r:id="rId7"/>
+    <sheet name="RPfE (not exported)" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,6 +35,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="232">
   <si>
     <t>Source:</t>
   </si>
@@ -660,9 +662,6 @@
     <t>BCoISC-WACCbI  Weighted Average Cost of Capital by Industry</t>
   </si>
   <si>
-    <t>BCoISC-RPfE  Risk Premium for Equity</t>
-  </si>
-  <si>
     <t>Weighted Average Cost of Debt</t>
   </si>
   <si>
@@ -673,6 +672,117 @@
   </si>
   <si>
     <t>This variable expresses the financing cost of capital/debt by industry.</t>
+  </si>
+  <si>
+    <t>Pretax WACC Build - multi-vintage beta average</t>
+  </si>
+  <si>
+    <t>Purpose: EPS discounts PRETAX cash flows (no industry income tax in the fuel choice), so the decision-side WACC must be pretax. Damodaran published Cost of Capital (NYU Data col K) is AFTER-tax.</t>
+  </si>
+  <si>
+    <t>Method: Cost of Equity = risk-free + mean(beta across 4 vintages) x ERP, using the CURRENT Jan-2026 risk-free rate and ERP (NYU Data D9 / D10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Pretax WACC = E/(D+E) x Cost of Equity + D/(D+E) x PRETAX Cost of Debt (NYU Data col G). Leverage is current-vintage.</t>
+  </si>
+  <si>
+    <t>Why average betas: single-vintage regression betas are noisy and mean-revert. Four consecutive vintages show a systematic decline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        (e.g. Oil/Gas Integrated 0.978 -&gt; 0.671 -&gt; 0.484 -&gt; 0.299) which produced implausible sector WACCs, including one BELOW its own cost of debt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        A 4-vintage mean agrees closely with standard Blume/Bloomberg shrinkage (0.67*raw + 0.33*1.0) for every affected sector.</t>
+  </si>
+  <si>
+    <t>Beta sources = col C of each vintage Industry Averages sheet, https://pages.stern.nyu.edu/~adamodar/pc/ :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Jan2023 = archives/wacc22.xls | Jan2024 = archives/wacc23.xls | Jan2025 = archives/wacc24.xls | Jan2026 = datasets/wacc.xls (matches NYU Data tab)</t>
+  </si>
+  <si>
+    <t>Beta Jan2023</t>
+  </si>
+  <si>
+    <t>Beta Jan2024</t>
+  </si>
+  <si>
+    <t>Beta Jan2025</t>
+  </si>
+  <si>
+    <t>Beta Jan2026</t>
+  </si>
+  <si>
+    <t>Mean Beta</t>
+  </si>
+  <si>
+    <t>Pretax Cost of Debt</t>
+  </si>
+  <si>
+    <t>Pretax WACC</t>
+  </si>
+  <si>
+    <t>BCoISC-RPfE  Risk Premium for Equity  [REFERENCE ONLY - not exported, not read by EPS.mdl]</t>
+  </si>
+  <si>
+    <t>Tax basis (important - the two exported files are NOT on the same basis by accident)</t>
+  </si>
+  <si>
+    <t>FIRbI = PRETAX cost of debt (Damodaran "Cost of Debt", NYU Data col G). Pretax is correct here: FIRbI drives actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   loan repayments, which EPS books as revenue to ISIC 64T66 (financial and insurance activities). A lender receives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   pretax interest, so the repayment cash flow must be pretax.</t>
+  </si>
+  <si>
+    <t>WACCbI = PRETAX weighted average cost of capital, built on the "Pretax WACC Build" tab. NOT Damodaran col K,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   which is an AFTER-tax WACC (it uses his after-tax cost of debt). EPS discounts pretax cash flows - the industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   fuel choice models no corporate income tax on fuel, carbon tax, or capital - so a pretax WACC is the consistent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   decision rate. Using his after-tax WACC understated required return, which both inflated the present value of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   future fuel savings and understated annualized capital cost.</t>
+  </si>
+  <si>
+    <t>Consequence of the old mismatch: WACCbI minus FIRbI looked implausibly thin (+0.19 to +3.3pp) and was NEGATIVE for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   rubber and plastic products (1.931% WACC vs 2.723% cost of debt) - impossible on a common basis. All 25 rows now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   clear their own cost of debt.</t>
+  </si>
+  <si>
+    <t>COUPLING - read before editing WACCbI values:</t>
+  </si>
+  <si>
+    <t>HRPfIEP Hurdle Rate Premium for Industrial Equipment Purchases (InputData/indst/HRPfIEP) is defined as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   0.20 minus the MEAN of the 25 real WACC values in BCoISC-WACCbI.csv, so that the decision hurdle rate hits a 20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   target. Any change to these WACC values requires recomputing HRPfIEP or the target silently drifts.</t>
+  </si>
+  <si>
+    <t>Cost of equity by industry is computed on the "Pretax WACC Build" tab (column J) and is deliberately NOT exported to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   a CSV, to avoid creating another orphaned input file. It is the intended hook if a future revision splits the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   financed share (cost of debt) from the unfinanced share (cost of equity).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Old mean 0.04483 -&gt; HRPfIEP 0.15520.   New mean 0.05245 -&gt; HRPfIEP 0.147546, exported rounded to 0.1475.</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F0629E-7DF7-4E6A-B1DA-78D3050B5FAD}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="87.140625" customWidth="1"/>
@@ -2145,12 +2255,12 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2196,7 +2306,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2248,12 +2358,115 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18">
       <c r="A26" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -7152,20 +7365,20 @@
         <v>83</v>
       </c>
       <c r="G3" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C3,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.2728474173721983E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C3,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.5239224225506385E-2</v>
       </c>
       <c r="H3" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D3,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D3,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I3" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E3,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E3,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K3" s="46">
         <f>AVERAGE(G3:I3)</f>
-        <v>7.2728474173721983E-2</v>
+        <v>7.5239224225506385E-2</v>
       </c>
     </row>
     <row r="4" spans="2:11">
@@ -7176,20 +7389,20 @@
         <v>69</v>
       </c>
       <c r="G4" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C4,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>8.4094140364796094E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C4,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>9.2177653727149589E-2</v>
       </c>
       <c r="H4" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D4,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D4,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I4" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E4,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E4,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K4" s="46">
         <f t="shared" ref="K4:K27" si="0">AVERAGE(G4:I4)</f>
-        <v>8.4094140364796094E-2</v>
+        <v>9.2177653727149589E-2</v>
       </c>
     </row>
     <row r="5" spans="2:11">
@@ -7200,20 +7413,20 @@
         <v>105</v>
       </c>
       <c r="G5" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C5,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.2476190336964839E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C5,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.3222738678316135E-2</v>
       </c>
       <c r="H5" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D5,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D5,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I5" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E5,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E5,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K5" s="46">
         <f t="shared" si="0"/>
-        <v>6.2476190336964839E-2</v>
+        <v>7.3222738678316135E-2</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -7224,20 +7437,20 @@
         <v>102</v>
       </c>
       <c r="G6" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C6,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>8.1973866470970574E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C6,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.4926930752977539E-2</v>
       </c>
       <c r="H6" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D6,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D6,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E6,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E6,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K6" s="46">
         <f t="shared" si="0"/>
-        <v>8.1973866470970574E-2</v>
+        <v>8.4926930752977539E-2</v>
       </c>
     </row>
     <row r="7" spans="2:11">
@@ -7254,20 +7467,20 @@
         <v>139</v>
       </c>
       <c r="G7" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C7,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>5.7893819913489727E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C7,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>6.3106774182182593E-2</v>
       </c>
       <c r="H7" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D7,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.5321556537096731E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D7,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.0994514165423711E-2</v>
       </c>
       <c r="I7" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E7,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.9363980217054505E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E7,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.8684446369281078E-2</v>
       </c>
       <c r="K7" s="46">
         <f t="shared" si="0"/>
-        <v>6.4193118889213654E-2</v>
+        <v>7.4261911572295794E-2</v>
       </c>
     </row>
     <row r="8" spans="2:11">
@@ -7278,20 +7491,20 @@
         <v>54</v>
       </c>
       <c r="G8" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C8,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.1335699230612268E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C8,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.0453161841801846E-2</v>
       </c>
       <c r="H8" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D8,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D8,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E8,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E8,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K8" s="46">
         <f t="shared" si="0"/>
-        <v>7.1335699230612268E-2</v>
+        <v>8.0453161841801846E-2</v>
       </c>
     </row>
     <row r="9" spans="2:11">
@@ -7302,20 +7515,20 @@
         <v>109</v>
       </c>
       <c r="G9" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C9,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.9291283507432896E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C9,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.5100812933388212E-2</v>
       </c>
       <c r="H9" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D9,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D9,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E9,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E9,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K9" s="46">
         <f t="shared" si="0"/>
-        <v>6.9291283507432896E-2</v>
+        <v>8.5100812933388212E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -7329,20 +7542,20 @@
         <v>112</v>
       </c>
       <c r="G10" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C10,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.9291283507432896E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C10,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.5100812933388212E-2</v>
       </c>
       <c r="H10" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D10,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>5.9470957360467105E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D10,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.1133151457873536E-2</v>
       </c>
       <c r="I10" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E10,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E10,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K10" s="46">
         <f t="shared" si="0"/>
-        <v>6.4381120433950001E-2</v>
+        <v>7.8116982195630874E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11">
@@ -7353,20 +7566,20 @@
         <v>104</v>
       </c>
       <c r="G11" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C11,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>5.0739665895732783E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C11,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>6.4260545060686639E-2</v>
       </c>
       <c r="H11" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D11,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E11,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K11" s="46">
         <f t="shared" si="0"/>
-        <v>5.0739665895732783E-2</v>
+        <v>6.4260545060686639E-2</v>
       </c>
     </row>
     <row r="12" spans="2:11">
@@ -7383,20 +7596,20 @@
         <v>68</v>
       </c>
       <c r="G12" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C12,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.2238337279932075E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C12,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.1372033575764354E-2</v>
       </c>
       <c r="H12" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D12,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>5.2287201981691012E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D12,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>6.4356564660986187E-2</v>
       </c>
       <c r="I12" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E12,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.2456799435330232E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E12,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.8606773612265535E-2</v>
       </c>
       <c r="K12" s="46">
         <f t="shared" si="0"/>
-        <v>6.2327446232317778E-2</v>
+        <v>7.1445123949672021E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11">
@@ -7407,20 +7620,20 @@
         <v>127</v>
       </c>
       <c r="G13" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C13,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>4.479472762848332E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C13,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>5.6522924599543486E-2</v>
       </c>
       <c r="H13" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D13,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E13,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K13" s="46">
         <f t="shared" si="0"/>
-        <v>4.479472762848332E-2</v>
+        <v>5.6522924599543486E-2</v>
       </c>
     </row>
     <row r="14" spans="2:11">
@@ -7431,20 +7644,20 @@
         <v>63</v>
       </c>
       <c r="G14" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C14,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.8536557455491568E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C14,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.664026837220512E-2</v>
       </c>
       <c r="H14" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D14,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E14,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K14" s="46">
         <f t="shared" si="0"/>
-        <v>7.8536557455491568E-2</v>
+        <v>8.664026837220512E-2</v>
       </c>
     </row>
     <row r="15" spans="2:11">
@@ -7455,20 +7668,20 @@
         <v>63</v>
       </c>
       <c r="G15" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C15,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.8536557455491568E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C15,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.664026837220512E-2</v>
       </c>
       <c r="H15" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D15,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E15,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K15" s="46">
         <f t="shared" si="0"/>
-        <v>7.8536557455491568E-2</v>
+        <v>8.664026837220512E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11">
@@ -7479,20 +7692,20 @@
         <v>135</v>
       </c>
       <c r="G16" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C16,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.7594142068806174E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C16,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.3075906735793029E-2</v>
       </c>
       <c r="H16" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D16,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E16,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K16" s="46">
         <f t="shared" si="0"/>
-        <v>7.7594142068806174E-2</v>
+        <v>8.3075906735793029E-2</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -7503,20 +7716,20 @@
         <v>102</v>
       </c>
       <c r="G17" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C17,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>8.1973866470970574E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C17,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.4926930752977539E-2</v>
       </c>
       <c r="H17" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D17,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E17,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K17" s="46">
         <f t="shared" si="0"/>
-        <v>8.1973866470970574E-2</v>
+        <v>8.4926930752977539E-2</v>
       </c>
     </row>
     <row r="18" spans="2:11">
@@ -7527,20 +7740,20 @@
         <v>102</v>
       </c>
       <c r="G18" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C18,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>8.1973866470970574E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C18,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.4926930752977539E-2</v>
       </c>
       <c r="H18" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D18,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E18,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K18" s="46">
         <f t="shared" si="0"/>
-        <v>8.1973866470970574E-2</v>
+        <v>8.4926930752977539E-2</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -7554,20 +7767,20 @@
         <v>79</v>
       </c>
       <c r="G19" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C19,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.6313570521383822E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C19,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.9319311219074549E-2</v>
       </c>
       <c r="H19" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D19,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.8548315008803479E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D19,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.2662841478072832E-2</v>
       </c>
       <c r="I19" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E19,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E19,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K19" s="46">
         <f t="shared" si="0"/>
-        <v>7.7430942765093658E-2</v>
+        <v>8.5991076348573697E-2</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -7581,20 +7794,20 @@
         <v>77</v>
       </c>
       <c r="G20" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C20,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.5348525661416135E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C20,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.5352251192433772E-2</v>
       </c>
       <c r="H20" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D20,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>8.9925203619899932E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D20,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>9.4993387589159484E-2</v>
       </c>
       <c r="I20" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E20,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E20,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K20" s="46">
         <f t="shared" si="0"/>
-        <v>7.7636864640658027E-2</v>
+        <v>8.5172819390796628E-2</v>
       </c>
     </row>
     <row r="21" spans="2:11">
@@ -7605,20 +7818,20 @@
         <v>101</v>
       </c>
       <c r="G21" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C21,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.6995656373169588E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C21,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.2843828778605869E-2</v>
       </c>
       <c r="H21" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D21,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E21,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K21" s="46">
         <f t="shared" si="0"/>
-        <v>7.6995656373169588E-2</v>
+        <v>8.2843828778605869E-2</v>
       </c>
     </row>
     <row r="22" spans="2:11">
@@ -7632,20 +7845,20 @@
         <v>142</v>
       </c>
       <c r="G22" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C22,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>6.7207845080084982E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C22,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.6834298259680647E-2</v>
       </c>
       <c r="H22" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D22,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.5216767530858333E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D22,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.457403472914074E-2</v>
       </c>
       <c r="I22" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E22,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E22,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K22" s="46">
         <f t="shared" si="0"/>
-        <v>7.1212306305471651E-2</v>
+        <v>8.0704166494410701E-2</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -7656,20 +7869,20 @@
         <v>141</v>
       </c>
       <c r="G23" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C23,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.2658793447523407E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C23,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>7.6901827551478522E-2</v>
       </c>
       <c r="H23" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D23,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E23,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K23" s="46">
         <f t="shared" si="0"/>
-        <v>7.2658793447523407E-2</v>
+        <v>7.6901827551478522E-2</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -7680,20 +7893,20 @@
         <v>101</v>
       </c>
       <c r="G24" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C24,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>7.6995656373169588E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C24,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.2843828778605869E-2</v>
       </c>
       <c r="H24" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D24,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E24,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K24" s="46">
         <f t="shared" si="0"/>
-        <v>7.6995656373169588E-2</v>
+        <v>8.2843828778605869E-2</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -7704,20 +7917,20 @@
         <v>106</v>
       </c>
       <c r="G25" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C25,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>5.7775581011015355E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C25,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>6.6173571523634928E-2</v>
       </c>
       <c r="H25" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D25,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E25,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K25" s="46">
         <f t="shared" si="0"/>
-        <v>5.7775581011015355E-2</v>
+        <v>6.6173571523634928E-2</v>
       </c>
     </row>
     <row r="26" spans="2:11">
@@ -7728,20 +7941,20 @@
         <v>144</v>
       </c>
       <c r="G26" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C26,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>4.9292156627376238E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C26,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>6.2809595857208689E-2</v>
       </c>
       <c r="H26" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D26,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E26,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K26" s="46">
         <f t="shared" si="0"/>
-        <v>4.9292156627376238E-2</v>
+        <v>6.2809595857208689E-2</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -7752,20 +7965,20 @@
         <v>80</v>
       </c>
       <c r="G27" s="45">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(C27,'NYU Data'!$A$20:$A$114,0)),"")</f>
-        <v>8.6855451614682708E-2</v>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(C27,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
+        <v>8.3741948700366969E-2</v>
       </c>
       <c r="H27" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(D27,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('Pretax WACC Build'!$K$11:$K$105,MATCH(E27,'Pretax WACC Build'!$A$11:$A$105,0)),"")</f>
         <v/>
       </c>
       <c r="K27" s="46">
         <f t="shared" si="0"/>
-        <v>8.6855451614682708E-2</v>
+        <v>8.3741948700366969E-2</v>
       </c>
     </row>
   </sheetData>
@@ -7787,6 +8000,3988 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D372893-7CA4-4678-9A8E-1F3D2B8D8E8B}">
+  <dimension ref="A1:K105"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11">
+        <v>1.6317379999999999</v>
+      </c>
+      <c r="C11">
+        <v>1.3723259999999999</v>
+      </c>
+      <c r="D11">
+        <v>1.337294</v>
+      </c>
+      <c r="E11">
+        <v>1.210507</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ref="F11:F42" si="0">IF(COUNT(B11:E11)=0,"",AVERAGE(B11:E11))</f>
+        <v>1.3879662499999998</v>
+      </c>
+      <c r="G11">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.71326642417939357</v>
+      </c>
+      <c r="H11">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.28673357582060643</v>
+      </c>
+      <c r="I11">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J11">
+        <f>IF(F11="","",'NYU Data'!$D$9+F11*'NYU Data'!$D$10)</f>
+        <v>0.10140329475</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ref="K11:K42" si="1">IF(OR(F11="",G11=""),"",G11*J11+H11*I11)</f>
+        <v>8.7499499143737322E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12">
+        <v>1.4141820000000001</v>
+      </c>
+      <c r="C12">
+        <v>1.0764050000000001</v>
+      </c>
+      <c r="D12">
+        <v>0.90155300000000005</v>
+      </c>
+      <c r="E12">
+        <v>0.94549099999999997</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>1.08440775</v>
+      </c>
+      <c r="G12">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A12,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.86533188033244401</v>
+      </c>
+      <c r="H12">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A12,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.13466811966755599</v>
+      </c>
+      <c r="I12">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A12,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J12">
+        <f>IF(F12="","",'NYU Data'!$D$9+F12*'NYU Data'!$D$10)</f>
+        <v>8.7864585649999993E-2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>8.3157721331114959E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>1.4159649999999999</v>
+      </c>
+      <c r="C13">
+        <v>1.26684</v>
+      </c>
+      <c r="D13">
+        <v>1.2360070000000001</v>
+      </c>
+      <c r="E13">
+        <v>1.185465</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>1.2760692499999999</v>
+      </c>
+      <c r="G13">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.5230930742546499</v>
+      </c>
+      <c r="H13">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.4769069257453501</v>
+      </c>
+      <c r="I13">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J13">
+        <f>IF(F13="","",'NYU Data'!$D$9+F13*'NYU Data'!$D$10)</f>
+        <v>9.641268855E-2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>7.5667385812739296E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14">
+        <v>1.324697</v>
+      </c>
+      <c r="C14">
+        <v>1.1947000000000001</v>
+      </c>
+      <c r="D14">
+        <v>0.990568</v>
+      </c>
+      <c r="E14">
+        <v>0.93587399999999998</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>1.1114597500000001</v>
+      </c>
+      <c r="G14">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.76165943862519259</v>
+      </c>
+      <c r="H14">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.23834056137480741</v>
+      </c>
+      <c r="I14">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J14">
+        <f>IF(F14="","",'NYU Data'!$D$9+F14*'NYU Data'!$D$10)</f>
+        <v>8.9071104849999999E-2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>8.0453161841801846E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>1.5405979999999999</v>
+      </c>
+      <c r="C15">
+        <v>1.522378</v>
+      </c>
+      <c r="D15">
+        <v>1.615413</v>
+      </c>
+      <c r="E15">
+        <v>1.456493</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>1.5337205</v>
+      </c>
+      <c r="G15">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.83545064476896913</v>
+      </c>
+      <c r="H15">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.16454935523103087</v>
+      </c>
+      <c r="I15">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J15">
+        <f>IF(F15="","",'NYU Data'!$D$9+F15*'NYU Data'!$D$10)</f>
+        <v>0.1079039343</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>9.8855211517383024E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16">
+        <v>1.473992</v>
+      </c>
+      <c r="C16">
+        <v>1.344427</v>
+      </c>
+      <c r="D16">
+        <v>1.2251240000000001</v>
+      </c>
+      <c r="E16">
+        <v>1.3394459999999999</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>1.3457472499999998</v>
+      </c>
+      <c r="G16">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.70689360734933704</v>
+      </c>
+      <c r="H16">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.29310639265066296</v>
+      </c>
+      <c r="I16">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J16">
+        <f>IF(F16="","",'NYU Data'!$D$9+F16*'NYU Data'!$D$10)</f>
+        <v>9.9520327349999993E-2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>8.5859421759352905E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17">
+        <v>1.0801019999999999</v>
+      </c>
+      <c r="C17">
+        <v>1.0613760000000001</v>
+      </c>
+      <c r="D17">
+        <v>0.87525299999999995</v>
+      </c>
+      <c r="E17">
+        <v>0.761046</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>0.94444424999999999</v>
+      </c>
+      <c r="G17">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.37851594436467451</v>
+      </c>
+      <c r="H17">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.62148405563532549</v>
+      </c>
+      <c r="I17">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J17">
+        <f>IF(F17="","",'NYU Data'!$D$9+F17*'NYU Data'!$D$10)</f>
+        <v>8.1622213550000003E-2</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>6.0295233978898091E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18">
+        <v>0.50487400000000004</v>
+      </c>
+      <c r="C18">
+        <v>0.46115800000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.51926099999999997</v>
+      </c>
+      <c r="E18">
+        <v>0.39847700000000003</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>0.47094249999999999</v>
+      </c>
+      <c r="G18">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.65745228553598767</v>
+      </c>
+      <c r="H18">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.34254771446401233</v>
+      </c>
+      <c r="I18">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J18">
+        <f>IF(F18="","",'NYU Data'!$D$9+F18*'NYU Data'!$D$10)</f>
+        <v>6.0504035499999997E-2</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>5.5983078604060099E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19">
+        <v>1.012974</v>
+      </c>
+      <c r="C19">
+        <v>1.1318349999999999</v>
+      </c>
+      <c r="D19">
+        <v>0.61029800000000001</v>
+      </c>
+      <c r="E19">
+        <v>0.81247599999999998</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>0.89189574999999999</v>
+      </c>
+      <c r="G19">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A19,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.69764972142048753</v>
+      </c>
+      <c r="H19">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A19,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.30235027857951247</v>
+      </c>
+      <c r="I19">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A19,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J19">
+        <f>IF(F19="","",'NYU Data'!$D$9+F19*'NYU Data'!$D$10)</f>
+        <v>7.9278550449999999E-2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>7.1306918926540314E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20">
+        <v>1.3034429999999999</v>
+      </c>
+      <c r="C20">
+        <v>0.76414599999999999</v>
+      </c>
+      <c r="D20">
+        <v>0.56776599999999999</v>
+      </c>
+      <c r="E20">
+        <v>0.64146899999999996</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>0.81920599999999988</v>
+      </c>
+      <c r="G20">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A20,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.82927597261423158</v>
+      </c>
+      <c r="H20">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A20,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.17072402738576842</v>
+      </c>
+      <c r="I20">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A20,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J20">
+        <f>IF(F20="","",'NYU Data'!$D$9+F20*'NYU Data'!$D$10)</f>
+        <v>7.6036587599999997E-2</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>7.2088835597320378E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21">
+        <v>1.3220590000000001</v>
+      </c>
+      <c r="C21">
+        <v>1.060924</v>
+      </c>
+      <c r="D21">
+        <v>0.91752400000000001</v>
+      </c>
+      <c r="E21">
+        <v>0.470752</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>0.94281475000000015</v>
+      </c>
+      <c r="G21">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.53805591362114591</v>
+      </c>
+      <c r="H21">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.46194408637885409</v>
+      </c>
+      <c r="I21">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J21">
+        <f>IF(F21="","",'NYU Data'!$D$9+F21*'NYU Data'!$D$10)</f>
+        <v>8.1549537850000006E-2</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>6.8321058535828288E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22">
+        <v>1.2048080000000001</v>
+      </c>
+      <c r="C22">
+        <v>1.1203259999999999</v>
+      </c>
+      <c r="D22">
+        <v>0.95226699999999997</v>
+      </c>
+      <c r="E22">
+        <v>1.171457</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>1.1122145000000001</v>
+      </c>
+      <c r="G22">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A22,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.42449573823876963</v>
+      </c>
+      <c r="H22">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A22,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.57550426176123037</v>
+      </c>
+      <c r="I22">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A22,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J22">
+        <f>IF(F22="","",'NYU Data'!$D$9+F22*'NYU Data'!$D$10)</f>
+        <v>8.9104766700000004E-2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>6.6986545672874903E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23">
+        <v>1.27728</v>
+      </c>
+      <c r="C23">
+        <v>1.3177989999999999</v>
+      </c>
+      <c r="D23">
+        <v>1.359883</v>
+      </c>
+      <c r="E23">
+        <v>1.111532</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>1.2666235000000001</v>
+      </c>
+      <c r="G23">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.79366147706163681</v>
+      </c>
+      <c r="H23">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.20633852293836319</v>
+      </c>
+      <c r="I23">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J23">
+        <f>IF(F23="","",'NYU Data'!$D$9+F23*'NYU Data'!$D$10)</f>
+        <v>9.5991408100000009E-2</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>8.664026837220512E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24">
+        <v>1.17092</v>
+      </c>
+      <c r="C24">
+        <v>1.0221020000000001</v>
+      </c>
+      <c r="D24">
+        <v>1.0038499999999999</v>
+      </c>
+      <c r="E24">
+        <v>0.88797899999999996</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>1.0212127499999999</v>
+      </c>
+      <c r="G24">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.83530953528892349</v>
+      </c>
+      <c r="H24">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.16469046471107651</v>
+      </c>
+      <c r="I24">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J24">
+        <f>IF(F24="","",'NYU Data'!$D$9+F24*'NYU Data'!$D$10)</f>
+        <v>8.504608864999999E-2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>7.9385004016211749E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25">
+        <v>1.2551639999999999</v>
+      </c>
+      <c r="C25">
+        <v>1.2767980000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.960511</v>
+      </c>
+      <c r="E25">
+        <v>0.74074399999999996</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>1.0583042499999999</v>
+      </c>
+      <c r="G25">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.40495756914925196</v>
+      </c>
+      <c r="H25">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.59504243085074804</v>
+      </c>
+      <c r="I25">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J25">
+        <f>IF(F25="","",'NYU Data'!$D$9+F25*'NYU Data'!$D$10)</f>
+        <v>8.6700369549999989E-2</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>6.5261960953378925E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26">
+        <v>1.247101</v>
+      </c>
+      <c r="C26">
+        <v>1.0962670000000001</v>
+      </c>
+      <c r="D26">
+        <v>1.1476869999999999</v>
+      </c>
+      <c r="E26">
+        <v>1.0122469999999999</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>1.1258254999999999</v>
+      </c>
+      <c r="G26">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.50162029462192392</v>
+      </c>
+      <c r="H26">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.49837970537807608</v>
+      </c>
+      <c r="I26">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J26">
+        <f>IF(F26="","",'NYU Data'!$D$9+F26*'NYU Data'!$D$10)</f>
+        <v>8.9711817299999996E-2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>7.1372033575764354E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27">
+        <v>1.4125909999999999</v>
+      </c>
+      <c r="C27">
+        <v>1.1332800000000001</v>
+      </c>
+      <c r="D27">
+        <v>0.99413899999999999</v>
+      </c>
+      <c r="E27">
+        <v>0.85070299999999999</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>1.09767825</v>
+      </c>
+      <c r="G27">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.36217451038972182</v>
+      </c>
+      <c r="H27">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.63782548961027818</v>
+      </c>
+      <c r="I27">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J27">
+        <f>IF(F27="","",'NYU Data'!$D$9+F27*'NYU Data'!$D$10)</f>
+        <v>8.8456449950000002E-2</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>6.4356564660986187E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28">
+        <v>1.2772950000000001</v>
+      </c>
+      <c r="C28">
+        <v>1.087383</v>
+      </c>
+      <c r="D28">
+        <v>0.92154899999999995</v>
+      </c>
+      <c r="E28">
+        <v>0.96978299999999995</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>1.0640025</v>
+      </c>
+      <c r="G28">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A28,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.76992392360340145</v>
+      </c>
+      <c r="H28">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A28,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.23007607639659855</v>
+      </c>
+      <c r="I28">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A28,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J28">
+        <f>IF(F28="","",'NYU Data'!$D$9+F28*'NYU Data'!$D$10)</f>
+        <v>8.6954511499999998E-2</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>7.8606773612265535E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29">
+        <v>1.4521790000000001</v>
+      </c>
+      <c r="C29">
+        <v>1.2707580000000001</v>
+      </c>
+      <c r="D29">
+        <v>1.1820630000000001</v>
+      </c>
+      <c r="E29">
+        <v>1.0709930000000001</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>1.2439982500000002</v>
+      </c>
+      <c r="G29">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A29,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.93333222184603304</v>
+      </c>
+      <c r="H29">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A29,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.6667778153966961E-2</v>
+      </c>
+      <c r="I29">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A29,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J29">
+        <f>IF(F29="","",'NYU Data'!$D$9+F29*'NYU Data'!$D$10)</f>
+        <v>9.4982321950000004E-2</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>9.2177653727149589E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30">
+        <v>1.171387</v>
+      </c>
+      <c r="C30">
+        <v>0.99732399999999999</v>
+      </c>
+      <c r="D30">
+        <v>1.234461</v>
+      </c>
+      <c r="E30">
+        <v>1.0878559999999999</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>1.122757</v>
+      </c>
+      <c r="G30">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A30,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.79935972823036783</v>
+      </c>
+      <c r="H30">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A30,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.20064027176963217</v>
+      </c>
+      <c r="I30">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A30,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J30">
+        <f>IF(F30="","",'NYU Data'!$D$9+F30*'NYU Data'!$D$10)</f>
+        <v>8.9574962199999997E-2</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>8.2219096140584022E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31">
+        <v>1.291086</v>
+      </c>
+      <c r="C31">
+        <v>1.132922</v>
+      </c>
+      <c r="D31">
+        <v>1.1422460000000001</v>
+      </c>
+      <c r="E31">
+        <v>1.3503289999999999</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>1.2291457499999998</v>
+      </c>
+      <c r="G31">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A31,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.95579689621950636</v>
+      </c>
+      <c r="H31">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A31,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.4203103780493636E-2</v>
+      </c>
+      <c r="I31">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A31,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J31">
+        <f>IF(F31="","",'NYU Data'!$D$9+F31*'NYU Data'!$D$10)</f>
+        <v>9.4319900449999994E-2</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>9.2489586932180068E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32">
+        <v>1.2643960000000001</v>
+      </c>
+      <c r="C32">
+        <v>1.1279619999999999</v>
+      </c>
+      <c r="D32">
+        <v>1.2936369999999999</v>
+      </c>
+      <c r="E32">
+        <v>1.1503559999999999</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>1.2090877499999999</v>
+      </c>
+      <c r="G32">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A32,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.85018145475128581</v>
+      </c>
+      <c r="H32">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A32,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.14981854524871419</v>
+      </c>
+      <c r="I32">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A32,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J32">
+        <f>IF(F32="","",'NYU Data'!$D$9+F32*'NYU Data'!$D$10)</f>
+        <v>9.3425313649999994E-2</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>8.7020074394395006E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33">
+        <v>1.0382279999999999</v>
+      </c>
+      <c r="C33">
+        <v>1.1948540000000001</v>
+      </c>
+      <c r="D33">
+        <v>1.089996</v>
+      </c>
+      <c r="E33">
+        <v>0.88095500000000004</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>1.05100825</v>
+      </c>
+      <c r="G33">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A33,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.86540598442853023</v>
+      </c>
+      <c r="H33">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A33,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.13459401557146977</v>
+      </c>
+      <c r="I33">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A33,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J33">
+        <f>IF(F33="","",'NYU Data'!$D$9+F33*'NYU Data'!$D$10)</f>
+        <v>8.6374967949999992E-2</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>8.1116518669376428E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34">
+        <v>1.2417419999999999</v>
+      </c>
+      <c r="C34">
+        <v>1.1233550000000001</v>
+      </c>
+      <c r="D34">
+        <v>1.2519480000000001</v>
+      </c>
+      <c r="E34">
+        <v>1.135265</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>1.1880774999999999</v>
+      </c>
+      <c r="G34">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A34,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.88464406300874721</v>
+      </c>
+      <c r="H34">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A34,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.11535593699125279</v>
+      </c>
+      <c r="I34">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A34,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J34">
+        <f>IF(F34="","",'NYU Data'!$D$9+F34*'NYU Data'!$D$10)</f>
+        <v>9.2488256500000005E-2</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>8.8763037637943631E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35">
+        <v>1.268006</v>
+      </c>
+      <c r="C35">
+        <v>1.0269619999999999</v>
+      </c>
+      <c r="D35">
+        <v>1.0737969999999999</v>
+      </c>
+      <c r="E35">
+        <v>0.98283299999999996</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>1.0878995</v>
+      </c>
+      <c r="G35">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A35,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.87307973621673463</v>
+      </c>
+      <c r="H35">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A35,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.12692026378326537</v>
+      </c>
+      <c r="I35">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A35,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J35">
+        <f>IF(F35="","",'NYU Data'!$D$9+F35*'NYU Data'!$D$10)</f>
+        <v>8.8020317700000003E-2</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>8.4488721037662848E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36">
+        <v>1.1008290000000001</v>
+      </c>
+      <c r="C36">
+        <v>1.2251860000000001</v>
+      </c>
+      <c r="D36">
+        <v>0.98317200000000005</v>
+      </c>
+      <c r="E36">
+        <v>0.78090599999999999</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>1.0225232500000001</v>
+      </c>
+      <c r="G36">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A36,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.803996597945147</v>
+      </c>
+      <c r="H36">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A36,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.196003402054853</v>
+      </c>
+      <c r="I36">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A36,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J36">
+        <f>IF(F36="","",'NYU Data'!$D$9+F36*'NYU Data'!$D$10)</f>
+        <v>8.5104536950000004E-2</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>7.8794886190425503E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37">
+        <v>1.589669</v>
+      </c>
+      <c r="C37">
+        <v>1.2410540000000001</v>
+      </c>
+      <c r="D37">
+        <v>1.2697510000000001</v>
+      </c>
+      <c r="E37">
+        <v>1.2511239999999999</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>1.3378995</v>
+      </c>
+      <c r="G37">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A37,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.89283140312053133</v>
+      </c>
+      <c r="H37">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A37,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.10716859687946867</v>
+      </c>
+      <c r="I37">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A37,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J37">
+        <f>IF(F37="","",'NYU Data'!$D$9+F37*'NYU Data'!$D$10)</f>
+        <v>9.917031770000001E-2</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>9.4993387589159484E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38">
+        <v>1.5389189999999999</v>
+      </c>
+      <c r="C38">
+        <v>1.2951790000000001</v>
+      </c>
+      <c r="D38">
+        <v>0.91963499999999998</v>
+      </c>
+      <c r="E38">
+        <v>0.86597800000000003</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>1.1549277499999999</v>
+      </c>
+      <c r="G38">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A38,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.94514104725576553</v>
+      </c>
+      <c r="H38">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A38,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.4858952744234468E-2</v>
+      </c>
+      <c r="I38">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A38,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J38">
+        <f>IF(F38="","",'NYU Data'!$D$9+F38*'NYU Data'!$D$10)</f>
+        <v>9.1009777649999998E-2</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>8.9319311219074549E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39">
+        <v>1.2012529999999999</v>
+      </c>
+      <c r="C39">
+        <v>0.93395499999999998</v>
+      </c>
+      <c r="D39">
+        <v>1.0582320000000001</v>
+      </c>
+      <c r="E39">
+        <v>0.97147700000000003</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>1.04122925</v>
+      </c>
+      <c r="G39">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A39,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.90080541162666683</v>
+      </c>
+      <c r="H39">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A39,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>9.919458837333317E-2</v>
+      </c>
+      <c r="I39">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A39,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J39">
+        <f>IF(F39="","",'NYU Data'!$D$9+F39*'NYU Data'!$D$10)</f>
+        <v>8.5938824550000001E-2</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>8.2662841478072832E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40">
+        <v>1.1967639999999999</v>
+      </c>
+      <c r="C40">
+        <v>0.96064400000000005</v>
+      </c>
+      <c r="D40">
+        <v>0.98791499999999999</v>
+      </c>
+      <c r="E40">
+        <v>1.209972</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>1.08882375</v>
+      </c>
+      <c r="G40">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A40,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.87710469220614817</v>
+      </c>
+      <c r="H40">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A40,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.12289530779385183</v>
+      </c>
+      <c r="I40">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A40,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J40">
+        <f>IF(F40="","",'NYU Data'!$D$9+F40*'NYU Data'!$D$10)</f>
+        <v>8.8061539250000001E-2</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>8.3741948700366969E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41">
+        <v>1.4497949999999999</v>
+      </c>
+      <c r="C41">
+        <v>0.99455899999999997</v>
+      </c>
+      <c r="D41">
+        <v>1.0409090000000001</v>
+      </c>
+      <c r="E41">
+        <v>0.82516999999999996</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>1.0776082499999999</v>
+      </c>
+      <c r="G41">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A41,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.86270959003227576</v>
+      </c>
+      <c r="H41">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A41,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.13729040996772424</v>
+      </c>
+      <c r="I41">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A41,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J41">
+        <f>IF(F41="","",'NYU Data'!$D$9+F41*'NYU Data'!$D$10)</f>
+        <v>8.756132794999999E-2</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>8.2804444801048344E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42">
+        <v>1.0153449999999999</v>
+      </c>
+      <c r="C42">
+        <v>0.906999</v>
+      </c>
+      <c r="D42">
+        <v>0.92047000000000001</v>
+      </c>
+      <c r="E42">
+        <v>0.94548100000000002</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>0.94707374999999994</v>
+      </c>
+      <c r="G42">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A42,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.82340128768470366</v>
+      </c>
+      <c r="H42">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A42,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.17659871231529634</v>
+      </c>
+      <c r="I42">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A42,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J42">
+        <f>IF(F42="","",'NYU Data'!$D$9+F42*'NYU Data'!$D$10)</f>
+        <v>8.1739489249999991E-2</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>7.6648768367879261E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43">
+        <v>1.140314</v>
+      </c>
+      <c r="C43">
+        <v>0.99162499999999998</v>
+      </c>
+      <c r="D43">
+        <v>0.98238800000000004</v>
+      </c>
+      <c r="E43">
+        <v>1.1291739999999999</v>
+      </c>
+      <c r="F43">
+        <f t="shared" ref="F43:F74" si="2">IF(COUNT(B43:E43)=0,"",AVERAGE(B43:E43))</f>
+        <v>1.06087525</v>
+      </c>
+      <c r="G43">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A43,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.65855113028384804</v>
+      </c>
+      <c r="H43">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A43,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.34144886971615196</v>
+      </c>
+      <c r="I43">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A43,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J43">
+        <f>IF(F43="","",'NYU Data'!$D$9+F43*'NYU Data'!$D$10)</f>
+        <v>8.6815036149999997E-2</v>
+      </c>
+      <c r="K43">
+        <f t="shared" ref="K43:K74" si="3">IF(OR(F43="",G43=""),"",G43*J43+H43*I43)</f>
+        <v>7.5239224225506385E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44">
+        <v>0.88572499999999998</v>
+      </c>
+      <c r="C44">
+        <v>1.143508</v>
+      </c>
+      <c r="D44">
+        <v>1.0734900000000001</v>
+      </c>
+      <c r="E44">
+        <v>0.96971300000000005</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="2"/>
+        <v>1.0181089999999999</v>
+      </c>
+      <c r="G44">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A44,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.2687233190210403</v>
+      </c>
+      <c r="H44">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A44,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.7312766809789597</v>
+      </c>
+      <c r="I44">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A44,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J44">
+        <f>IF(F44="","",'NYU Data'!$D$9+F44*'NYU Data'!$D$10)</f>
+        <v>8.4907661400000001E-2</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="3"/>
+        <v>5.9871920560288512E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45">
+        <v>0.91752</v>
+      </c>
+      <c r="C45">
+        <v>0.60571799999999998</v>
+      </c>
+      <c r="D45">
+        <v>0.47423999999999999</v>
+      </c>
+      <c r="E45">
+        <v>0.60745300000000002</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="2"/>
+        <v>0.65123275000000003</v>
+      </c>
+      <c r="G45">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A45,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.69573029958954236</v>
+      </c>
+      <c r="H45">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A45,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.30426970041045764</v>
+      </c>
+      <c r="I45">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A45,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J45">
+        <f>IF(F45="","",'NYU Data'!$D$9+F45*'NYU Data'!$D$10)</f>
+        <v>6.8544980650000004E-2</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="3"/>
+        <v>6.3106774182182593E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46">
+        <v>1.1237060000000001</v>
+      </c>
+      <c r="C46">
+        <v>0.96571099999999999</v>
+      </c>
+      <c r="D46">
+        <v>0.72463200000000005</v>
+      </c>
+      <c r="E46">
+        <v>0.86664200000000002</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="2"/>
+        <v>0.92017275000000009</v>
+      </c>
+      <c r="G46">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A46,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.68041767533092656</v>
+      </c>
+      <c r="H46">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A46,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.31958232466907344</v>
+      </c>
+      <c r="I46">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A46,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J46">
+        <f>IF(F46="","",'NYU Data'!$D$9+F46*'NYU Data'!$D$10)</f>
+        <v>8.0539704650000002E-2</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="3"/>
+        <v>7.0994514165423711E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47">
+        <v>1.270896</v>
+      </c>
+      <c r="C47">
+        <v>1.1071059999999999</v>
+      </c>
+      <c r="D47">
+        <v>0.86624299999999999</v>
+      </c>
+      <c r="E47">
+        <v>0.82315799999999995</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="2"/>
+        <v>1.0168507499999999</v>
+      </c>
+      <c r="G47">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A47,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.70257590887206756</v>
+      </c>
+      <c r="H47">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A47,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.29742409112793244</v>
+      </c>
+      <c r="I47">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A47,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J47">
+        <f>IF(F47="","",'NYU Data'!$D$9+F47*'NYU Data'!$D$10)</f>
+        <v>8.4851543449999997E-2</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="3"/>
+        <v>7.5352251192433772E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48">
+        <v>1.6007009999999999</v>
+      </c>
+      <c r="C48">
+        <v>1.106708</v>
+      </c>
+      <c r="D48">
+        <v>1.130425</v>
+      </c>
+      <c r="E48">
+        <v>0.85633000000000004</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="2"/>
+        <v>1.1735409999999999</v>
+      </c>
+      <c r="G48">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A48,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.46924210179760639</v>
+      </c>
+      <c r="H48">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A48,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.53075789820239361</v>
+      </c>
+      <c r="I48">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A48,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J48">
+        <f>IF(F48="","",'NYU Data'!$D$9+F48*'NYU Data'!$D$10)</f>
+        <v>9.1839928600000009E-2</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="3"/>
+        <v>7.5044132807499192E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49">
+        <v>1.1623829999999999</v>
+      </c>
+      <c r="C49">
+        <v>1.0620799999999999</v>
+      </c>
+      <c r="D49">
+        <v>1.0145169999999999</v>
+      </c>
+      <c r="E49">
+        <v>0.90856099999999995</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="2"/>
+        <v>1.0368852499999999</v>
+      </c>
+      <c r="G49">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A49,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.88664148204560789</v>
+      </c>
+      <c r="H49">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A49,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.11335851795439211</v>
+      </c>
+      <c r="I49">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A49,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J49">
+        <f>IF(F49="","",'NYU Data'!$D$9+F49*'NYU Data'!$D$10)</f>
+        <v>8.5745082149999999E-2</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="3"/>
+        <v>8.2023285976119159E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50">
+        <v>1.1603650000000001</v>
+      </c>
+      <c r="C50">
+        <v>1.0326230000000001</v>
+      </c>
+      <c r="D50">
+        <v>0.94121299999999997</v>
+      </c>
+      <c r="E50">
+        <v>0.87195400000000001</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="2"/>
+        <v>1.0015387499999999</v>
+      </c>
+      <c r="G50">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A50,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.73841435881638406</v>
+      </c>
+      <c r="H50">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A50,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.26158564118361594</v>
+      </c>
+      <c r="I50">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A50,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J50">
+        <f>IF(F50="","",'NYU Data'!$D$9+F50*'NYU Data'!$D$10)</f>
+        <v>8.4168628249999988E-2</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="3"/>
+        <v>7.5992604693627008E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51">
+        <v>1.471509</v>
+      </c>
+      <c r="C51">
+        <v>1.2747539999999999</v>
+      </c>
+      <c r="D51">
+        <v>1.2229239999999999</v>
+      </c>
+      <c r="E51">
+        <v>1.1083339999999999</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="2"/>
+        <v>1.26938025</v>
+      </c>
+      <c r="G51">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A51,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.86399549964940126</v>
+      </c>
+      <c r="H51">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A51,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.13600450035059874</v>
+      </c>
+      <c r="I51">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A51,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J51">
+        <f>IF(F51="","",'NYU Data'!$D$9+F51*'NYU Data'!$D$10)</f>
+        <v>9.6114359149999995E-2</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="3"/>
+        <v>9.0238779884337483E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52">
+        <v>1.5022070000000001</v>
+      </c>
+      <c r="C52">
+        <v>1.3695349999999999</v>
+      </c>
+      <c r="D52">
+        <v>1.427487</v>
+      </c>
+      <c r="E52">
+        <v>0.91061800000000004</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="2"/>
+        <v>1.3024617500000002</v>
+      </c>
+      <c r="G52">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A52,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.82410235304763335</v>
+      </c>
+      <c r="H52">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A52,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.17589764695236665</v>
+      </c>
+      <c r="I52">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A52,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J52">
+        <f>IF(F52="","",'NYU Data'!$D$9+F52*'NYU Data'!$D$10)</f>
+        <v>9.7589794050000012E-2</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="3"/>
+        <v>8.9337064476409267E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53">
+        <v>1.1740010000000001</v>
+      </c>
+      <c r="C53">
+        <v>0.87957600000000002</v>
+      </c>
+      <c r="D53">
+        <v>0.85708200000000001</v>
+      </c>
+      <c r="E53">
+        <v>0.799678</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="2"/>
+        <v>0.92758425000000011</v>
+      </c>
+      <c r="G53">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A53,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.62531115482012134</v>
+      </c>
+      <c r="H53">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A53,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.37468884517987866</v>
+      </c>
+      <c r="I53">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A53,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J53">
+        <f>IF(F53="","",'NYU Data'!$D$9+F53*'NYU Data'!$D$10)</f>
+        <v>8.0870257550000005E-2</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="3"/>
+        <v>7.0394985004194055E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54">
+        <v>1.4599770000000001</v>
+      </c>
+      <c r="C54">
+        <v>1.3434280000000001</v>
+      </c>
+      <c r="D54">
+        <v>1.1937610000000001</v>
+      </c>
+      <c r="E54">
+        <v>1.080368</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="2"/>
+        <v>1.2693835</v>
+      </c>
+      <c r="G54">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A54,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.71556246801374979</v>
+      </c>
+      <c r="H54">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A54,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.28443753198625021</v>
+      </c>
+      <c r="I54">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A54,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J54">
+        <f>IF(F54="","",'NYU Data'!$D$9+F54*'NYU Data'!$D$10)</f>
+        <v>9.6114504099999998E-2</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="3"/>
+        <v>8.3188950386520938E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55">
+        <v>1.1550009999999999</v>
+      </c>
+      <c r="C55">
+        <v>0.84344399999999997</v>
+      </c>
+      <c r="D55">
+        <v>0.89526499999999998</v>
+      </c>
+      <c r="E55">
+        <v>0.81551600000000002</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="2"/>
+        <v>0.92730649999999992</v>
+      </c>
+      <c r="G55">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A55,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.84639870791279104</v>
+      </c>
+      <c r="H55">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A55,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.15360129208720896</v>
+      </c>
+      <c r="I55">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A55,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J55">
+        <f>IF(F55="","",'NYU Data'!$D$9+F55*'NYU Data'!$D$10)</f>
+        <v>8.085786989999999E-2</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="3"/>
+        <v>7.656550177615104E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56">
+        <v>1.4047130000000001</v>
+      </c>
+      <c r="C56">
+        <v>0.93074299999999999</v>
+      </c>
+      <c r="D56">
+        <v>0.98448899999999995</v>
+      </c>
+      <c r="E56">
+        <v>0.92056700000000002</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="2"/>
+        <v>1.060128</v>
+      </c>
+      <c r="G56">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A56,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.75092072801834941</v>
+      </c>
+      <c r="H56">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A56,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.24907927198165059</v>
+      </c>
+      <c r="I56">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A56,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J56">
+        <f>IF(F56="","",'NYU Data'!$D$9+F56*'NYU Data'!$D$10)</f>
+        <v>8.6781708799999996E-2</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="3"/>
+        <v>7.7787528820626589E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57">
+        <v>1.2277610000000001</v>
+      </c>
+      <c r="C57">
+        <v>1.0331490000000001</v>
+      </c>
+      <c r="D57">
+        <v>0.76036400000000004</v>
+      </c>
+      <c r="E57">
+        <v>0.67197499999999999</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="2"/>
+        <v>0.92331224999999995</v>
+      </c>
+      <c r="G57">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A57,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.79600333990423344</v>
+      </c>
+      <c r="H57">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A57,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.20399666009576656</v>
+      </c>
+      <c r="I57">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A57,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J57">
+        <f>IF(F57="","",'NYU Data'!$D$9+F57*'NYU Data'!$D$10)</f>
+        <v>8.0679726350000008E-2</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="3"/>
+        <v>7.5015406912806892E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58">
+        <v>0.93935400000000002</v>
+      </c>
+      <c r="C58">
+        <v>0.76576100000000002</v>
+      </c>
+      <c r="D58">
+        <v>0.73167199999999999</v>
+      </c>
+      <c r="E58">
+        <v>0.64449299999999998</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="2"/>
+        <v>0.77032000000000012</v>
+      </c>
+      <c r="G58">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A58,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.59580596298176169</v>
+      </c>
+      <c r="H58">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A58,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.40419403701823831</v>
+      </c>
+      <c r="I58">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A58,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J58">
+        <f>IF(F58="","",'NYU Data'!$D$9+F58*'NYU Data'!$D$10)</f>
+        <v>7.3856272000000001E-2</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="3"/>
+        <v>6.44853275049911E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59">
+        <v>0.80330100000000004</v>
+      </c>
+      <c r="C59">
+        <v>0.73875800000000003</v>
+      </c>
+      <c r="D59">
+        <v>0.60566399999999998</v>
+      </c>
+      <c r="E59">
+        <v>0.48410999999999998</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="2"/>
+        <v>0.65795824999999997</v>
+      </c>
+      <c r="G59">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A59,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.87085797110051288</v>
+      </c>
+      <c r="H59">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A59,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.12914202889948712</v>
+      </c>
+      <c r="I59">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A59,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J59">
+        <f>IF(F59="","",'NYU Data'!$D$9+F59*'NYU Data'!$D$10)</f>
+        <v>6.8844937950000004E-2</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="3"/>
+        <v>6.6063355802796847E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60">
+        <v>0.62361299999999997</v>
+      </c>
+      <c r="C60">
+        <v>0.45700499999999999</v>
+      </c>
+      <c r="D60">
+        <v>0.56713599999999997</v>
+      </c>
+      <c r="E60">
+        <v>0.659582</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="2"/>
+        <v>0.57683399999999996</v>
+      </c>
+      <c r="G60">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A60,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.75364660406139838</v>
+      </c>
+      <c r="H60">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A60,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.24635339593860162</v>
+      </c>
+      <c r="I60">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A60,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J60">
+        <f>IF(F60="","",'NYU Data'!$D$9+F60*'NYU Data'!$D$10)</f>
+        <v>6.5226796399999995E-2</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="3"/>
+        <v>6.1641172879665064E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>101</v>
+      </c>
+      <c r="B61">
+        <v>1.224817</v>
+      </c>
+      <c r="C61">
+        <v>1.0260560000000001</v>
+      </c>
+      <c r="D61">
+        <v>1.067242</v>
+      </c>
+      <c r="E61">
+        <v>0.96362099999999995</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="2"/>
+        <v>1.0704340000000001</v>
+      </c>
+      <c r="G61">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A61,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.87189810166984505</v>
+      </c>
+      <c r="H61">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A61,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.12810189833015495</v>
+      </c>
+      <c r="I61">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A61,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J61">
+        <f>IF(F61="","",'NYU Data'!$D$9+F61*'NYU Data'!$D$10)</f>
+        <v>8.7241356399999997E-2</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="3"/>
+        <v>8.2843828778605869E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62">
+        <v>1.2900529999999999</v>
+      </c>
+      <c r="C62">
+        <v>0.96247799999999994</v>
+      </c>
+      <c r="D62">
+        <v>1.022251</v>
+      </c>
+      <c r="E62">
+        <v>1.043031</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="2"/>
+        <v>1.07945325</v>
+      </c>
+      <c r="G62">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A62,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.90102654716927866</v>
+      </c>
+      <c r="H62">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A62,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>9.8973452830721342E-2</v>
+      </c>
+      <c r="I62">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A62,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J62">
+        <f>IF(F62="","",'NYU Data'!$D$9+F62*'NYU Data'!$D$10)</f>
+        <v>8.7643614950000004E-2</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="3"/>
+        <v>8.4926930752977539E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63">
+        <v>1.177095</v>
+      </c>
+      <c r="C63">
+        <v>1.139419</v>
+      </c>
+      <c r="D63">
+        <v>1.200496</v>
+      </c>
+      <c r="E63">
+        <v>1.3343750000000001</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="2"/>
+        <v>1.2128462500000001</v>
+      </c>
+      <c r="G63">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A63,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.67520815630511344</v>
+      </c>
+      <c r="H63">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A63,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.32479184369488656</v>
+      </c>
+      <c r="I63">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A63,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J63">
+        <f>IF(F63="","",'NYU Data'!$D$9+F63*'NYU Data'!$D$10)</f>
+        <v>9.3592942750000005E-2</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="3"/>
+        <v>7.9652570621104826E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>104</v>
+      </c>
+      <c r="B64">
+        <v>0.97748599999999997</v>
+      </c>
+      <c r="C64">
+        <v>0.67065200000000003</v>
+      </c>
+      <c r="D64">
+        <v>0.483682</v>
+      </c>
+      <c r="E64">
+        <v>0.29938199999999998</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="2"/>
+        <v>0.60780049999999997</v>
+      </c>
+      <c r="G64">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A64,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.87838725930586903</v>
+      </c>
+      <c r="H64">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A64,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.12161274069413097</v>
+      </c>
+      <c r="I64">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A64,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J64">
+        <f>IF(F64="","",'NYU Data'!$D$9+F64*'NYU Data'!$D$10)</f>
+        <v>6.6607902299999994E-2</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="3"/>
+        <v>6.4260545060686639E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65">
+        <v>1.2574320000000001</v>
+      </c>
+      <c r="C65">
+        <v>0.92989900000000003</v>
+      </c>
+      <c r="D65">
+        <v>0.87592899999999996</v>
+      </c>
+      <c r="E65">
+        <v>0.72140599999999999</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="2"/>
+        <v>0.94616650000000013</v>
+      </c>
+      <c r="G65">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A65,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.72680954826276589</v>
+      </c>
+      <c r="H65">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A65,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.27319045173723411</v>
+      </c>
+      <c r="I65">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A65,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J65">
+        <f>IF(F65="","",'NYU Data'!$D$9+F65*'NYU Data'!$D$10)</f>
+        <v>8.16990259E-2</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="3"/>
+        <v>7.3222738678316135E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>106</v>
+      </c>
+      <c r="B66">
+        <v>0.991255</v>
+      </c>
+      <c r="C66">
+        <v>0.79075200000000001</v>
+      </c>
+      <c r="D66">
+        <v>0.75470800000000005</v>
+      </c>
+      <c r="E66">
+        <v>0.66922199999999998</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="2"/>
+        <v>0.80148425000000001</v>
+      </c>
+      <c r="G66">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A66,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.63080682460107163</v>
+      </c>
+      <c r="H66">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A66,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.36919317539892837</v>
+      </c>
+      <c r="I66">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A66,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J66">
+        <f>IF(F66="","",'NYU Data'!$D$9+F66*'NYU Data'!$D$10)</f>
+        <v>7.5246197550000005E-2</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="3"/>
+        <v>6.6173571523634928E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67">
+        <v>1.375159</v>
+      </c>
+      <c r="C67">
+        <v>0.97955000000000003</v>
+      </c>
+      <c r="D67">
+        <v>0.93760100000000002</v>
+      </c>
+      <c r="E67">
+        <v>0.95124200000000003</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="2"/>
+        <v>1.0608880000000001</v>
+      </c>
+      <c r="G67">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A67,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.72801067139535347</v>
+      </c>
+      <c r="H67">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A67,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.27198932860464653</v>
+      </c>
+      <c r="I67">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A67,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J67">
+        <f>IF(F67="","",'NYU Data'!$D$9+F67*'NYU Data'!$D$10)</f>
+        <v>8.6815604800000001E-2</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="3"/>
+        <v>7.7594458082499346E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68">
+        <v>0.95242199999999999</v>
+      </c>
+      <c r="C68">
+        <v>1.132722</v>
+      </c>
+      <c r="D68">
+        <v>0.97636299999999998</v>
+      </c>
+      <c r="E68">
+        <v>1.02193</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="2"/>
+        <v>1.02085925</v>
+      </c>
+      <c r="G68">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A68,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.64470545590217365</v>
+      </c>
+      <c r="H68">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A68,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.35529454409782635</v>
+      </c>
+      <c r="I68">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A68,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J68">
+        <f>IF(F68="","",'NYU Data'!$D$9+F68*'NYU Data'!$D$10)</f>
+        <v>8.5030322550000009E-2</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="3"/>
+        <v>7.1627076568198403E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>109</v>
+      </c>
+      <c r="B69">
+        <v>1.3830070000000001</v>
+      </c>
+      <c r="C69">
+        <v>1.938223</v>
+      </c>
+      <c r="D69">
+        <v>1.0717410000000001</v>
+      </c>
+      <c r="E69">
+        <v>0.957978</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="2"/>
+        <v>1.33773725</v>
+      </c>
+      <c r="G69">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A69,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.6959514879510198</v>
+      </c>
+      <c r="H69">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A69,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.3040485120489802</v>
+      </c>
+      <c r="I69">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A69,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J69">
+        <f>IF(F69="","",'NYU Data'!$D$9+F69*'NYU Data'!$D$10)</f>
+        <v>9.9163081350000001E-2</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="3"/>
+        <v>8.5100812933388212E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+      <c r="B70">
+        <v>0.72500100000000001</v>
+      </c>
+      <c r="C70">
+        <v>0.65062699999999996</v>
+      </c>
+      <c r="D70">
+        <v>0.54234899999999997</v>
+      </c>
+      <c r="E70">
+        <v>0.482433</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="2"/>
+        <v>0.60010249999999998</v>
+      </c>
+      <c r="G70">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A70,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.57422207892503341</v>
+      </c>
+      <c r="H70">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A70,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.42577792107496659</v>
+      </c>
+      <c r="I70">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A70,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J70">
+        <f>IF(F70="","",'NYU Data'!$D$9+F70*'NYU Data'!$D$10)</f>
+        <v>6.6264571500000008E-2</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="3"/>
+        <v>5.8192430340178888E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71">
+        <v>1.233619</v>
+      </c>
+      <c r="C71">
+        <v>0.86895100000000003</v>
+      </c>
+      <c r="D71">
+        <v>1.228315</v>
+      </c>
+      <c r="E71">
+        <v>0.836561</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="2"/>
+        <v>1.0418615</v>
+      </c>
+      <c r="G71">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A71,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.93213059887545091</v>
+      </c>
+      <c r="H71">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A71,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.7869401124549089E-2</v>
+      </c>
+      <c r="I71">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A71,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J71">
+        <f>IF(F71="","",'NYU Data'!$D$9+F71*'NYU Data'!$D$10)</f>
+        <v>8.5967022899999995E-2</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="3"/>
+        <v>8.4217891140008841E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72">
+        <v>1.1148960000000001</v>
+      </c>
+      <c r="C72">
+        <v>0.96111400000000002</v>
+      </c>
+      <c r="D72">
+        <v>0.63735299999999995</v>
+      </c>
+      <c r="E72">
+        <v>0.56300700000000004</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="2"/>
+        <v>0.8190925</v>
+      </c>
+      <c r="G72">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A72,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.80684283536273349</v>
+      </c>
+      <c r="H72">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A72,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.19315716463726651</v>
+      </c>
+      <c r="I72">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A72,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J72">
+        <f>IF(F72="","",'NYU Data'!$D$9+F72*'NYU Data'!$D$10)</f>
+        <v>7.6031525500000002E-2</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="3"/>
+        <v>7.1133151457873536E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73">
+        <v>1.0633760000000001</v>
+      </c>
+      <c r="C73">
+        <v>1.0315829999999999</v>
+      </c>
+      <c r="D73">
+        <v>0.94722700000000004</v>
+      </c>
+      <c r="E73">
+        <v>0.64179799999999998</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="2"/>
+        <v>0.92099600000000004</v>
+      </c>
+      <c r="G73">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A73,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.54211415599544854</v>
+      </c>
+      <c r="H73">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A73,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.45788584400455146</v>
+      </c>
+      <c r="I73">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A73,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J73">
+        <f>IF(F73="","",'NYU Data'!$D$9+F73*'NYU Data'!$D$10)</f>
+        <v>8.0576421600000003E-2</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="3"/>
+        <v>6.5342366525296749E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74">
+        <v>1.5166919999999999</v>
+      </c>
+      <c r="C74">
+        <v>0.66859400000000002</v>
+      </c>
+      <c r="D74">
+        <v>1.0261880000000001</v>
+      </c>
+      <c r="E74">
+        <v>0.84356600000000004</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="2"/>
+        <v>1.01376</v>
+      </c>
+      <c r="G74">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A74,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.4954680163706453</v>
+      </c>
+      <c r="H74">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A74,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.5045319836293547</v>
+      </c>
+      <c r="I74">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A74,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J74">
+        <f>IF(F74="","",'NYU Data'!$D$9+F74*'NYU Data'!$D$10)</f>
+        <v>8.4713696000000005E-2</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="3"/>
+        <v>6.8669227766325919E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75">
+        <v>0.78980300000000003</v>
+      </c>
+      <c r="C75">
+        <v>0.56357199999999996</v>
+      </c>
+      <c r="D75">
+        <v>0.86419400000000002</v>
+      </c>
+      <c r="E75">
+        <v>0.80998599999999998</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ref="F75:F105" si="4">IF(COUNT(B75:E75)=0,"",AVERAGE(B75:E75))</f>
+        <v>0.75688875</v>
+      </c>
+      <c r="G75">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A75,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.65121044647557569</v>
+      </c>
+      <c r="H75">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A75,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.34878955352442431</v>
+      </c>
+      <c r="I75">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A75,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J75">
+        <f>IF(F75="","",'NYU Data'!$D$9+F75*'NYU Data'!$D$10)</f>
+        <v>7.3257238249999995E-2</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ref="K75:K105" si="5">IF(OR(F75="",G75=""),"",G75*J75+H75*I75)</f>
+        <v>6.537974308453974E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76">
+        <v>1.3454839999999999</v>
+      </c>
+      <c r="C76">
+        <v>1.0801190000000001</v>
+      </c>
+      <c r="D76">
+        <v>1.0752170000000001</v>
+      </c>
+      <c r="E76">
+        <v>0.96549700000000005</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="4"/>
+        <v>1.11657925</v>
+      </c>
+      <c r="G76">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A76,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.80229597034020494</v>
+      </c>
+      <c r="H76">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A76,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.19770402965979506</v>
+      </c>
+      <c r="I76">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A76,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J76">
+        <f>IF(F76="","",'NYU Data'!$D$9+F76*'NYU Data'!$D$10)</f>
+        <v>8.9299434550000001E-2</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="5"/>
+        <v>8.2105689814512606E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77">
+        <v>1.4179809999999999</v>
+      </c>
+      <c r="C77">
+        <v>1.171287</v>
+      </c>
+      <c r="D77">
+        <v>1.3278970000000001</v>
+      </c>
+      <c r="E77">
+        <v>1.0234730000000001</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="4"/>
+        <v>1.2351595</v>
+      </c>
+      <c r="G77">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A77,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.61353257079825152</v>
+      </c>
+      <c r="H77">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A77,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.38646742920174848</v>
+      </c>
+      <c r="I77">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A77,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J77">
+        <f>IF(F77="","",'NYU Data'!$D$9+F77*'NYU Data'!$D$10)</f>
+        <v>9.4588113700000004E-2</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="5"/>
+        <v>7.8482039646670443E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78">
+        <v>0.82924799999999999</v>
+      </c>
+      <c r="C78">
+        <v>0.65514399999999995</v>
+      </c>
+      <c r="D78">
+        <v>0.53732999999999997</v>
+      </c>
+      <c r="E78">
+        <v>0.58133199999999996</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="4"/>
+        <v>0.65076350000000005</v>
+      </c>
+      <c r="G78">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A78,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.69702329435031385</v>
+      </c>
+      <c r="H78">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A78,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.30297670564968615</v>
+      </c>
+      <c r="I78">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A78,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J78">
+        <f>IF(F78="","",'NYU Data'!$D$9+F78*'NYU Data'!$D$10)</f>
+        <v>6.852405210000001E-2</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="5"/>
+        <v>6.2095476574438604E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" t="s">
+        <v>119</v>
+      </c>
+      <c r="B79">
+        <v>1.410398</v>
+      </c>
+      <c r="C79">
+        <v>1.194577</v>
+      </c>
+      <c r="D79">
+        <v>1.0090399999999999</v>
+      </c>
+      <c r="E79">
+        <v>0.92408699999999999</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="4"/>
+        <v>1.1345255000000001</v>
+      </c>
+      <c r="G79">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A79,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.78604107236352705</v>
+      </c>
+      <c r="H79">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A79,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.21395892763647295</v>
+      </c>
+      <c r="I79">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A79,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J79">
+        <f>IF(F79="","",'NYU Data'!$D$9+F79*'NYU Data'!$D$10)</f>
+        <v>9.0099837300000013E-2</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="5"/>
+        <v>8.1663899512266672E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" t="s">
+        <v>120</v>
+      </c>
+      <c r="B80">
+        <v>1.5201929999999999</v>
+      </c>
+      <c r="C80">
+        <v>1.494496</v>
+      </c>
+      <c r="D80">
+        <v>1.3530740000000001</v>
+      </c>
+      <c r="E80">
+        <v>0.93601500000000004</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="4"/>
+        <v>1.3259445000000001</v>
+      </c>
+      <c r="G80">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A80,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.68796896276521902</v>
+      </c>
+      <c r="H80">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A80,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.31203103723478098</v>
+      </c>
+      <c r="I80">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A80,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J80">
+        <f>IF(F80="","",'NYU Data'!$D$9+F80*'NYU Data'!$D$10)</f>
+        <v>9.8637124699999995E-2</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="5"/>
+        <v>8.3670517088763385E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81">
+        <v>1.789172</v>
+      </c>
+      <c r="C81">
+        <v>1.9381790000000001</v>
+      </c>
+      <c r="D81">
+        <v>1.7927740000000001</v>
+      </c>
+      <c r="E81">
+        <v>1.535309</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="4"/>
+        <v>1.7638585</v>
+      </c>
+      <c r="G81">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A81,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.81110093418688756</v>
+      </c>
+      <c r="H81">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A81,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.18889906581311244</v>
+      </c>
+      <c r="I81">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A81,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J81">
+        <f>IF(F81="","",'NYU Data'!$D$9+F81*'NYU Data'!$D$10)</f>
+        <v>0.11816808910000001</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="5"/>
+        <v>0.1058414637294586</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" t="s">
+        <v>122</v>
+      </c>
+      <c r="B82">
+        <v>1.2752460000000001</v>
+      </c>
+      <c r="C82">
+        <v>1.1060430000000001</v>
+      </c>
+      <c r="D82">
+        <v>1.117156</v>
+      </c>
+      <c r="E82">
+        <v>0.948434</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="4"/>
+        <v>1.11171975</v>
+      </c>
+      <c r="G82">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A82,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.77980999195158307</v>
+      </c>
+      <c r="H82">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A82,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.22019000804841693</v>
+      </c>
+      <c r="I82">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A82,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J82">
+        <f>IF(F82="","",'NYU Data'!$D$9+F82*'NYU Data'!$D$10)</f>
+        <v>8.9082700850000002E-2</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="5"/>
+        <v>8.0625048320693171E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83">
+        <v>1.3632139999999999</v>
+      </c>
+      <c r="C83">
+        <v>1.246677</v>
+      </c>
+      <c r="D83">
+        <v>1.0617719999999999</v>
+      </c>
+      <c r="E83">
+        <v>0.80524099999999998</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="4"/>
+        <v>1.1192260000000001</v>
+      </c>
+      <c r="G83">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A83,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.92640899521910824</v>
+      </c>
+      <c r="H83">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A83,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>7.3591004780891756E-2</v>
+      </c>
+      <c r="I83">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A83,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J83">
+        <f>IF(F83="","",'NYU Data'!$D$9+F83*'NYU Data'!$D$10)</f>
+        <v>8.9417479600000002E-2</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="5"/>
+        <v>8.6566160825518448E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84">
+        <v>0.66757</v>
+      </c>
+      <c r="C84">
+        <v>0.49360799999999999</v>
+      </c>
+      <c r="D84">
+        <v>0.57940700000000001</v>
+      </c>
+      <c r="E84">
+        <v>1.118304</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="4"/>
+        <v>0.71472225</v>
+      </c>
+      <c r="G84">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A84,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.658110474673126</v>
+      </c>
+      <c r="H84">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A84,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.341889525326874</v>
+      </c>
+      <c r="I84">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A84,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J84">
+        <f>IF(F84="","",'NYU Data'!$D$9+F84*'NYU Data'!$D$10)</f>
+        <v>7.1376612350000007E-2</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="5"/>
+        <v>6.5064096687839093E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" t="s">
+        <v>125</v>
+      </c>
+      <c r="C85">
+        <v>1.120868</v>
+      </c>
+      <c r="D85">
+        <v>0.94758900000000001</v>
+      </c>
+      <c r="E85">
+        <v>0.62073900000000004</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="4"/>
+        <v>0.89639866666666668</v>
+      </c>
+      <c r="G85">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A85,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.6393051931486502</v>
+      </c>
+      <c r="H85">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A85,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.3606948068513498</v>
+      </c>
+      <c r="I85">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A85,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J85">
+        <f>IF(F85="","",'NYU Data'!$D$9+F85*'NYU Data'!$D$10)</f>
+        <v>7.9479380533333338E-2</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="5"/>
+        <v>6.7874609256107693E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86">
+        <v>1.4752069999999999</v>
+      </c>
+      <c r="C86">
+        <v>1.181406</v>
+      </c>
+      <c r="D86">
+        <v>1.2239629999999999</v>
+      </c>
+      <c r="E86">
+        <v>1.0893999999999999</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="4"/>
+        <v>1.242494</v>
+      </c>
+      <c r="G86">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A86,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.83499651515131101</v>
+      </c>
+      <c r="H86">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A86,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.16500348484868899</v>
+      </c>
+      <c r="I86">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A86,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J86">
+        <f>IF(F86="","",'NYU Data'!$D$9+F86*'NYU Data'!$D$10)</f>
+        <v>9.4915232399999994E-2</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="5"/>
+        <v>8.7984717682575486E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87">
+        <v>0.83801499999999995</v>
+      </c>
+      <c r="C87">
+        <v>0.67452000000000001</v>
+      </c>
+      <c r="D87">
+        <v>0.64534499999999995</v>
+      </c>
+      <c r="E87">
+        <v>0.52942999999999996</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="4"/>
+        <v>0.67182750000000002</v>
+      </c>
+      <c r="G87">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A87,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.21811565703705116</v>
+      </c>
+      <c r="H87">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A87,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.78188434296294884</v>
+      </c>
+      <c r="I87">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A87,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J87">
+        <f>IF(F87="","",'NYU Data'!$D$9+F87*'NYU Data'!$D$10)</f>
+        <v>6.9463506499999994E-2</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="5"/>
+        <v>5.6522924599543486E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" t="s">
+        <v>128</v>
+      </c>
+      <c r="B88">
+        <v>1.6077459999999999</v>
+      </c>
+      <c r="C88">
+        <v>1.495241</v>
+      </c>
+      <c r="D88">
+        <v>1.4858720000000001</v>
+      </c>
+      <c r="E88">
+        <v>1.5181990000000001</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="4"/>
+        <v>1.5267644999999999</v>
+      </c>
+      <c r="G88">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A88,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.97474337819546364</v>
+      </c>
+      <c r="H88">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A88,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>2.5256621804536361E-2</v>
+      </c>
+      <c r="I88">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A88,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J88">
+        <f>IF(F88="","",'NYU Data'!$D$9+F88*'NYU Data'!$D$10)</f>
+        <v>0.10759369669999999</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="5"/>
+        <v>0.10621264702343954</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" t="s">
+        <v>129</v>
+      </c>
+      <c r="B89">
+        <v>1.7571429999999999</v>
+      </c>
+      <c r="C89">
+        <v>1.527982</v>
+      </c>
+      <c r="D89">
+        <v>1.4849760000000001</v>
+      </c>
+      <c r="E89">
+        <v>1.3972230000000001</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="4"/>
+        <v>1.5418310000000002</v>
+      </c>
+      <c r="G89">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A89,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.9536409808998203</v>
+      </c>
+      <c r="H89">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A89,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.6359019100179699E-2</v>
+      </c>
+      <c r="I89">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A89,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J89">
+        <f>IF(F89="","",'NYU Data'!$D$9+F89*'NYU Data'!$D$10)</f>
+        <v>0.10826566260000001</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="5"/>
+        <v>0.1056995674572808</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" t="s">
+        <v>130</v>
+      </c>
+      <c r="B90">
+        <v>0.94373899999999999</v>
+      </c>
+      <c r="C90">
+        <v>0.810836</v>
+      </c>
+      <c r="D90">
+        <v>0.57845000000000002</v>
+      </c>
+      <c r="E90">
+        <v>0.75293299999999996</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>0.77148950000000005</v>
+      </c>
+      <c r="G90">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A90,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.81599216268354535</v>
+      </c>
+      <c r="H90">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A90,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.18400783731645465</v>
+      </c>
+      <c r="I90">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A90,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J90">
+        <f>IF(F90="","",'NYU Data'!$D$9+F90*'NYU Data'!$D$10)</f>
+        <v>7.3908431699999999E-2</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="5"/>
+        <v>7.0045107719357666E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" t="s">
+        <v>131</v>
+      </c>
+      <c r="B91">
+        <v>1.327693</v>
+      </c>
+      <c r="C91">
+        <v>1.291579</v>
+      </c>
+      <c r="D91">
+        <v>1.4242079999999999</v>
+      </c>
+      <c r="E91">
+        <v>1.0173179999999999</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="4"/>
+        <v>1.2651995</v>
+      </c>
+      <c r="G91">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A91,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.89329798160715879</v>
+      </c>
+      <c r="H91">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A91,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.10670201839284121</v>
+      </c>
+      <c r="I91">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A91,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J91">
+        <f>IF(F91="","",'NYU Data'!$D$9+F91*'NYU Data'!$D$10)</f>
+        <v>9.59278977E-2</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="5"/>
+        <v>9.1338121294448418E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>132</v>
+      </c>
+      <c r="B92">
+        <v>1.3635759999999999</v>
+      </c>
+      <c r="C92">
+        <v>1.108331</v>
+      </c>
+      <c r="D92">
+        <v>1.182782</v>
+      </c>
+      <c r="E92">
+        <v>1.028311</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="4"/>
+        <v>1.17075</v>
+      </c>
+      <c r="G92">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A92,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.97996356872272972</v>
+      </c>
+      <c r="H92">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A92,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>2.0036431277270284E-2</v>
+      </c>
+      <c r="I92">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A92,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J92">
+        <f>IF(F92="","",'NYU Data'!$D$9+F92*'NYU Data'!$D$10)</f>
+        <v>9.1715450000000004E-2</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="5"/>
+        <v>9.0937987377185281E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>133</v>
+      </c>
+      <c r="B93">
+        <v>1.5513060000000001</v>
+      </c>
+      <c r="C93">
+        <v>1.6160840000000001</v>
+      </c>
+      <c r="D93">
+        <v>1.6870259999999999</v>
+      </c>
+      <c r="E93">
+        <v>1.6886760000000001</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="4"/>
+        <v>1.6357730000000001</v>
+      </c>
+      <c r="G93">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A93,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.89048058261622209</v>
+      </c>
+      <c r="H93">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A93,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.10951941738377791</v>
+      </c>
+      <c r="I93">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A93,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J93">
+        <f>IF(F93="","",'NYU Data'!$D$9+F93*'NYU Data'!$D$10)</f>
+        <v>0.11245547580000001</v>
+      </c>
+      <c r="K93">
+        <f t="shared" si="5"/>
+        <v>0.10593441854079631</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94">
+        <v>1.4697709999999999</v>
+      </c>
+      <c r="C94">
+        <v>1.293965</v>
+      </c>
+      <c r="D94">
+        <v>1.2417609999999999</v>
+      </c>
+      <c r="E94">
+        <v>1.276648</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="4"/>
+        <v>1.32053625</v>
+      </c>
+      <c r="G94">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A94,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.94717481124203029</v>
+      </c>
+      <c r="H94">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A94,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.282518875796971E-2</v>
+      </c>
+      <c r="I94">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A94,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J94">
+        <f>IF(F94="","",'NYU Data'!$D$9+F94*'NYU Data'!$D$10)</f>
+        <v>9.8395916750000006E-2</v>
+      </c>
+      <c r="K94">
+        <f t="shared" si="5"/>
+        <v>9.5993273087418229E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95">
+        <v>1.342484</v>
+      </c>
+      <c r="C95">
+        <v>1.1263719999999999</v>
+      </c>
+      <c r="D95">
+        <v>1.059779</v>
+      </c>
+      <c r="E95">
+        <v>1.062846</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="4"/>
+        <v>1.14787025</v>
+      </c>
+      <c r="G95">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A95,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.80963186390660424</v>
+      </c>
+      <c r="H95">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A95,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.19036813609339576</v>
+      </c>
+      <c r="I95">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A95,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J95">
+        <f>IF(F95="","",'NYU Data'!$D$9+F95*'NYU Data'!$D$10)</f>
+        <v>9.0695013150000003E-2</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="5"/>
+        <v>8.3075906735793029E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>136</v>
+      </c>
+      <c r="B96">
+        <v>1.0309740000000001</v>
+      </c>
+      <c r="C96">
+        <v>1.087361</v>
+      </c>
+      <c r="D96">
+        <v>0.77253899999999998</v>
+      </c>
+      <c r="E96">
+        <v>0.53813500000000003</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="4"/>
+        <v>0.85725225000000005</v>
+      </c>
+      <c r="G96">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A96,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.65812552349234665</v>
+      </c>
+      <c r="H96">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A96,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.34187447650765335</v>
+      </c>
+      <c r="I96">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A96,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J96">
+        <f>IF(F96="","",'NYU Data'!$D$9+F96*'NYU Data'!$D$10)</f>
+        <v>7.7733450350000011E-2</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="5"/>
+        <v>6.848183117805591E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>137</v>
+      </c>
+      <c r="B97">
+        <v>1.2331190000000001</v>
+      </c>
+      <c r="C97">
+        <v>1.0805070000000001</v>
+      </c>
+      <c r="D97">
+        <v>0.99961500000000003</v>
+      </c>
+      <c r="E97">
+        <v>0.92322000000000004</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="4"/>
+        <v>1.0591152500000001</v>
+      </c>
+      <c r="G97">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A97,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.91556018666934091</v>
+      </c>
+      <c r="H97">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A97,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>8.4439813330659086E-2</v>
+      </c>
+      <c r="I97">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A97,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J97">
+        <f>IF(F97="","",'NYU Data'!$D$9+F97*'NYU Data'!$D$10)</f>
+        <v>8.6736540150000013E-2</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="5"/>
+        <v>8.3880486733551959E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>138</v>
+      </c>
+      <c r="B98">
+        <v>0.88226800000000005</v>
+      </c>
+      <c r="C98">
+        <v>0.78450500000000001</v>
+      </c>
+      <c r="D98">
+        <v>0.88603900000000002</v>
+      </c>
+      <c r="E98">
+        <v>0.62871999999999995</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="4"/>
+        <v>0.79538300000000006</v>
+      </c>
+      <c r="G98">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A98,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.5100396006745912</v>
+      </c>
+      <c r="H98">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A98,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.4899603993254088</v>
+      </c>
+      <c r="I98">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A98,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J98">
+        <f>IF(F98="","",'NYU Data'!$D$9+F98*'NYU Data'!$D$10)</f>
+        <v>7.4974081800000009E-2</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="5"/>
+        <v>6.41650253517215E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99">
+        <v>2.0004569999999999</v>
+      </c>
+      <c r="C99">
+        <v>1.2232909999999999</v>
+      </c>
+      <c r="D99">
+        <v>0.97996799999999995</v>
+      </c>
+      <c r="E99">
+        <v>0.79431499999999999</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="4"/>
+        <v>1.24950775</v>
+      </c>
+      <c r="G99">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A99,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.81321637444562511</v>
+      </c>
+      <c r="H99">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A99,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.18678362555437489</v>
+      </c>
+      <c r="I99">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A99,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>6.0194999999999999E-2</v>
+      </c>
+      <c r="J99">
+        <f>IF(F99="","",'NYU Data'!$D$9+F99*'NYU Data'!$D$10)</f>
+        <v>9.5228045650000009E-2</v>
+      </c>
+      <c r="K99">
+        <f t="shared" si="5"/>
+        <v>8.8684446369281078E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>140</v>
+      </c>
+      <c r="B100">
+        <v>1.0582659999999999</v>
+      </c>
+      <c r="C100">
+        <v>1.2585310000000001</v>
+      </c>
+      <c r="D100">
+        <v>1.026899</v>
+      </c>
+      <c r="E100">
+        <v>0.85992199999999996</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="4"/>
+        <v>1.0509045000000001</v>
+      </c>
+      <c r="G100">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A100,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.73287154939615018</v>
+      </c>
+      <c r="H100">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A100,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.26712845060384982</v>
+      </c>
+      <c r="I100">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A100,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J100">
+        <f>IF(F100="","",'NYU Data'!$D$9+F100*'NYU Data'!$D$10)</f>
+        <v>8.6370340700000006E-2</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="5"/>
+        <v>7.6834298259680647E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>141</v>
+      </c>
+      <c r="B101">
+        <v>1.107831</v>
+      </c>
+      <c r="C101">
+        <v>1.017272</v>
+      </c>
+      <c r="D101">
+        <v>0.99185599999999996</v>
+      </c>
+      <c r="E101">
+        <v>0.97514599999999996</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="4"/>
+        <v>1.02302625</v>
+      </c>
+      <c r="G101">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A101,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.78252427065158103</v>
+      </c>
+      <c r="H101">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A101,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.21747572934841897</v>
+      </c>
+      <c r="I101">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A101,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J101">
+        <f>IF(F101="","",'NYU Data'!$D$9+F101*'NYU Data'!$D$10)</f>
+        <v>8.5126970750000003E-2</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="5"/>
+        <v>7.6901827551478522E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>142</v>
+      </c>
+      <c r="B102">
+        <v>1.5451239999999999</v>
+      </c>
+      <c r="C102">
+        <v>1.148407</v>
+      </c>
+      <c r="D102">
+        <v>1.104813</v>
+      </c>
+      <c r="E102">
+        <v>1.0113490000000001</v>
+      </c>
+      <c r="F102">
+        <f t="shared" si="4"/>
+        <v>1.2024232500000001</v>
+      </c>
+      <c r="G102">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A102,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.79852019226992521</v>
+      </c>
+      <c r="H102">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A102,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.20147980773007479</v>
+      </c>
+      <c r="I102">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A102,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.0671999999999995E-2</v>
+      </c>
+      <c r="J102">
+        <f>IF(F102="","",'NYU Data'!$D$9+F102*'NYU Data'!$D$10)</f>
+        <v>9.3128076949999999E-2</v>
+      </c>
+      <c r="K102">
+        <f t="shared" si="5"/>
+        <v>8.457403472914074E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>143</v>
+      </c>
+      <c r="B103">
+        <v>0.63513900000000001</v>
+      </c>
+      <c r="C103">
+        <v>0.58043199999999995</v>
+      </c>
+      <c r="D103">
+        <v>0.39343800000000001</v>
+      </c>
+      <c r="E103">
+        <v>0.23943500000000001</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="4"/>
+        <v>0.46211099999999999</v>
+      </c>
+      <c r="G103">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A103,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.55101188178185656</v>
+      </c>
+      <c r="H103">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A103,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.44898811821814344</v>
+      </c>
+      <c r="I103">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A103,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J103">
+        <f>IF(F103="","",'NYU Data'!$D$9+F103*'NYU Data'!$D$10)</f>
+        <v>6.0110150600000002E-2</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="5"/>
+        <v>5.4361239116724289E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>144</v>
+      </c>
+      <c r="B104">
+        <v>1.152415</v>
+      </c>
+      <c r="C104">
+        <v>0.71396300000000001</v>
+      </c>
+      <c r="D104">
+        <v>0.67856700000000003</v>
+      </c>
+      <c r="E104">
+        <v>0.41268300000000002</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="4"/>
+        <v>0.73940700000000004</v>
+      </c>
+      <c r="G104">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A104,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.61591735519626356</v>
+      </c>
+      <c r="H104">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A104,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.38408264480373644</v>
+      </c>
+      <c r="I104">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A104,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>4.7306000000000001E-2</v>
+      </c>
+      <c r="J104">
+        <f>IF(F104="","",'NYU Data'!$D$9+F104*'NYU Data'!$D$10)</f>
+        <v>7.2477552200000003E-2</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="5"/>
+        <v>6.2809595857208689E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105">
+        <v>1.15727</v>
+      </c>
+      <c r="C105">
+        <v>1.0002230000000001</v>
+      </c>
+      <c r="D105">
+        <v>1.00278</v>
+      </c>
+      <c r="E105">
+        <v>0.91211100000000001</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="4"/>
+        <v>1.0180960000000001</v>
+      </c>
+      <c r="G105">
+        <f>IFERROR(INDEX('NYU Data'!$E$20:$E$114,MATCH($A105,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.73980229704024358</v>
+      </c>
+      <c r="H105">
+        <f>IFERROR(INDEX('NYU Data'!$J$20:$J$114,MATCH($A105,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>0.26019770295975642</v>
+      </c>
+      <c r="I105">
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH($A105,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <v>5.2913000000000002E-2</v>
+      </c>
+      <c r="J105">
+        <f>IF(F105="","",'NYU Data'!$D$9+F105*'NYU Data'!$D$10)</f>
+        <v>8.4907081600000003E-2</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="5"/>
+        <v>7.6582295059373001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2EF6BF-246E-47B8-A508-66F5039B1799}">
   <dimension ref="B2:K27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7836,11 +12031,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H3" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D3,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D3,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I3" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E3,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E3,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K3" s="46">
@@ -7860,11 +12055,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H4" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D4,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D4,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I4" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E4,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E4,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K4" s="46">
@@ -7884,11 +12079,11 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="H5" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D5,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D5,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I5" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E5,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E5,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K5" s="46">
@@ -7908,11 +12103,11 @@
         <v>6.0194999999999999E-2</v>
       </c>
       <c r="H6" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D6,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D6,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E6,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E6,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K6" s="46">
@@ -7962,11 +12157,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H8" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D8,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D8,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E8,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E8,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K8" s="46">
@@ -7986,11 +12181,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H9" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D9,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D9,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E9,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E9,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K9" s="46">
@@ -8017,7 +12212,7 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="I10" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E10,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E10,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K10" s="46">
@@ -8037,11 +12232,11 @@
         <v>4.7306000000000001E-2</v>
       </c>
       <c r="H11" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D11,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E11,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E11,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K11" s="46">
@@ -8091,11 +12286,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H13" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D13,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E13,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E13,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K13" s="46">
@@ -8115,11 +12310,11 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="H14" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D14,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E14,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E14,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K14" s="46">
@@ -8139,11 +12334,11 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="H15" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D15,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E15,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E15,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K15" s="46">
@@ -8163,11 +12358,11 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="H16" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D16,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E16,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E16,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K16" s="46">
@@ -8187,11 +12382,11 @@
         <v>6.0194999999999999E-2</v>
       </c>
       <c r="H17" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D17,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E17,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E17,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K17" s="46">
@@ -8211,11 +12406,11 @@
         <v>6.0194999999999999E-2</v>
       </c>
       <c r="H18" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D18,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E18,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E18,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K18" s="46">
@@ -8242,7 +12437,7 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="I19" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E19,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E19,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K19" s="46">
@@ -8269,7 +12464,7 @@
         <v>6.0194999999999999E-2</v>
       </c>
       <c r="I20" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E20,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E20,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K20" s="46">
@@ -8289,11 +12484,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H21" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D21,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E21,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E21,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K21" s="46">
@@ -8320,7 +12515,7 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="I22" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E22,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E22,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K22" s="46">
@@ -8340,11 +12535,11 @@
         <v>4.7306000000000001E-2</v>
       </c>
       <c r="H23" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D23,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E23,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E23,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K23" s="46">
@@ -8364,11 +12559,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H24" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D24,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E24,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E24,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K24" s="46">
@@ -8388,11 +12583,11 @@
         <v>5.0671999999999995E-2</v>
       </c>
       <c r="H25" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D25,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E25,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E25,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K25" s="46">
@@ -8412,11 +12607,11 @@
         <v>4.7306000000000001E-2</v>
       </c>
       <c r="H26" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D26,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E26,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E26,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K26" s="46">
@@ -8436,11 +12631,11 @@
         <v>5.2913000000000002E-2</v>
       </c>
       <c r="H27" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(D27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(D27,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="45" t="str">
-        <f>IFERROR(INDEX('NYU Data'!$K$20:$K$114,MATCH(E27,'NYU Data'!$A$20:$A$114,0)),"")</f>
+        <f>IFERROR(INDEX('NYU Data'!$G$20:$G$114,MATCH(E27,'NYU Data'!$A$20:$A$114,0)),"")</f>
         <v/>
       </c>
       <c r="K27" s="46">
@@ -8465,7 +12660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0D2C3E-FEFB-4F66-9667-31E7FEED72E5}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -8505,7 +12700,7 @@
       </c>
       <c r="B2" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K3)/(1+'NYU Data'!C$17)-1</f>
-        <v>4.6564365047533807E-2</v>
+        <v>4.9013877293177188E-2</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -8514,7 +12709,7 @@
       </c>
       <c r="B3" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K4)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.7652819868093896E-2</v>
+        <v>6.5539174367950981E-2</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -8523,7 +12718,7 @@
       </c>
       <c r="B4" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K5)/(1+'NYU Data'!C$17)-1</f>
-        <v>3.6562136914112031E-2</v>
+        <v>4.7046574320308565E-2</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -8532,7 +12727,7 @@
       </c>
       <c r="B5" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K6)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.5584259971678707E-2</v>
+        <v>5.8465298295587997E-2</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -8541,7 +12736,7 @@
       </c>
       <c r="B6" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K7)/(1+'NYU Data'!C$17)-1</f>
-        <v>3.8237189160208684E-2</v>
+        <v>4.8060401533947195E-2</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -8550,7 +12745,7 @@
       </c>
       <c r="B7" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K8)/(1+'NYU Data'!C$17)-1</f>
-        <v>4.5205560224987673E-2</v>
+        <v>5.4100645699318939E-2</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -8559,7 +12754,7 @@
       </c>
       <c r="B8" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K9)/(1+'NYU Data'!C$17)-1</f>
-        <v>4.3211008299934628E-2</v>
+        <v>5.8634939447208101E-2</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -8568,7 +12763,7 @@
       </c>
       <c r="B9" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K10)/(1+'NYU Data'!C$17)-1</f>
-        <v>3.8420605301414668E-2</v>
+        <v>5.1821446044518105E-2</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -8577,7 +12772,7 @@
       </c>
       <c r="B10" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K11)/(1+'NYU Data'!C$17)-1</f>
-        <v>2.5111869166568823E-2</v>
+        <v>3.8302970790913715E-2</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -8586,7 +12781,7 @@
       </c>
       <c r="B11" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K12)/(1+'NYU Data'!C$17)-1</f>
-        <v>3.6417020714456516E-2</v>
+        <v>4.5312316048460533E-2</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -8595,7 +12790,7 @@
       </c>
       <c r="B12" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K13)/(1+'NYU Data'!C$17)-1</f>
-        <v>1.9311929393642346E-2</v>
+        <v>3.0754072780042607E-2</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -8604,7 +12799,7 @@
       </c>
       <c r="B13" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K14)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.2230787761455177E-2</v>
+        <v>6.0136847192395315E-2</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -8613,7 +12808,7 @@
       </c>
       <c r="B14" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K15)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.2230787761455177E-2</v>
+        <v>6.0136847192395315E-2</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -8622,7 +12817,7 @@
       </c>
       <c r="B15" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K16)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.131135811590859E-2</v>
+        <v>5.6659421205651928E-2</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -8631,7 +12826,7 @@
       </c>
       <c r="B16" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K17)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.5584259971678707E-2</v>
+        <v>5.8465298295587997E-2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8640,7 +12835,7 @@
       </c>
       <c r="B17" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K18)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.5584259971678707E-2</v>
+        <v>5.8465298295587997E-2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -8649,7 +12844,7 @@
       </c>
       <c r="B18" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K19)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.1152139283018316E-2</v>
+        <v>5.9503489120559694E-2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8658,7 +12853,7 @@
       </c>
       <c r="B19" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K20)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.1353038673812801E-2</v>
+        <v>5.8705189649557621E-2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -8667,7 +12862,7 @@
       </c>
       <c r="B20" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K21)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.0727469632360522E-2</v>
+        <v>5.6433003686444883E-2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -8676,7 +12871,7 @@
       </c>
       <c r="B21" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K22)/(1+'NYU Data'!C$17)-1</f>
-        <v>4.508517688338709E-2</v>
+        <v>5.4345528287229827E-2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -8685,7 +12880,7 @@
       </c>
       <c r="B22" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K23)/(1+'NYU Data'!C$17)-1</f>
-        <v>4.649638385124244E-2</v>
+        <v>5.0635929318515682E-2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -8694,7 +12889,7 @@
       </c>
       <c r="B23" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K24)/(1+'NYU Data'!C$17)-1</f>
-        <v>5.0727469632360522E-2</v>
+        <v>5.6433003686444883E-2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8703,7 +12898,7 @@
       </c>
       <c r="B24" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K25)/(1+'NYU Data'!C$17)-1</f>
-        <v>3.1976176596112627E-2</v>
+        <v>4.0169338071839089E-2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8712,7 +12907,7 @@
       </c>
       <c r="B25" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K26)/(1+'NYU Data'!C$17)-1</f>
-        <v>2.369966500231846E-2</v>
+        <v>3.688741059239864E-2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -8721,7 +12916,7 @@
       </c>
       <c r="B26" s="51">
         <f>(1+'EPS &lt;&gt; NYU Industry CoC Map'!K27)/(1+'NYU Data'!C$17)-1</f>
-        <v>6.0346782063105175E-2</v>
+        <v>5.7309218244260496E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8729,7 +12924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BA1585-54ED-4B8E-88D9-FA8A3C4B9460}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -8746,7 +12941,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D1" s="5"/>
       <c r="F1" s="5"/>
@@ -8993,7 +13188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B388480-FC75-4BF5-B02C-3AC172D606B8}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
